--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R373"/>
+  <dimension ref="A1:R375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>420.49</v>
+        <v>416.14</v>
       </c>
       <c r="C373" t="n">
         <v>408.35</v>
@@ -22680,18 +22680,138 @@
         <v>381.57</v>
       </c>
       <c r="N373" t="n">
-        <v>385.6</v>
+        <v>379.54</v>
       </c>
       <c r="O373" t="n">
-        <v>395</v>
+        <v>388.49</v>
       </c>
       <c r="P373" t="n">
         <v>392.93</v>
       </c>
       <c r="Q373" t="n">
-        <v>367.7</v>
+        <v>360.34</v>
       </c>
       <c r="R373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>414.84</v>
+      </c>
+      <c r="C374" t="n">
+        <v>408.15</v>
+      </c>
+      <c r="D374" t="n">
+        <v>399.35</v>
+      </c>
+      <c r="E374" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="F374" t="n">
+        <v>381.64</v>
+      </c>
+      <c r="G374" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="H374" t="n">
+        <v>369.33</v>
+      </c>
+      <c r="I374" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="J374" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="K374" t="n">
+        <v>367.88</v>
+      </c>
+      <c r="L374" t="n">
+        <v>374.29</v>
+      </c>
+      <c r="M374" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="N374" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="O374" t="n">
+        <v>385.07</v>
+      </c>
+      <c r="P374" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>354.53</v>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>415.23</v>
+      </c>
+      <c r="C375" t="n">
+        <v>409.38</v>
+      </c>
+      <c r="D375" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="E375" t="n">
+        <v>390.83</v>
+      </c>
+      <c r="F375" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="G375" t="n">
+        <v>357.1</v>
+      </c>
+      <c r="H375" t="n">
+        <v>369.8</v>
+      </c>
+      <c r="I375" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="J375" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="K375" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="L375" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="M375" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="N375" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="O375" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="P375" t="n">
+        <v>390.93</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="R375" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22708,7 +22828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26601,6 +26721,26 @@
       </c>
       <c r="B389" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -26769,28 +26909,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.211309188490014</v>
+        <v>-0.1906577219067555</v>
       </c>
       <c r="J2" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0129380474677423</v>
+        <v>0.01054686458394261</v>
       </c>
       <c r="M2" t="n">
-        <v>11.75322755814515</v>
+        <v>11.81227174200878</v>
       </c>
       <c r="N2" t="n">
-        <v>204.2157220685902</v>
+        <v>205.4601274919334</v>
       </c>
       <c r="O2" t="n">
-        <v>14.29040664461968</v>
+        <v>14.33388040594498</v>
       </c>
       <c r="P2" t="n">
-        <v>397.1007129874924</v>
+        <v>396.8803536377541</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26847,28 +26987,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08607227605030771</v>
+        <v>0.1029770267865945</v>
       </c>
       <c r="J3" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001831606132166042</v>
+        <v>0.002629358900276935</v>
       </c>
       <c r="M3" t="n">
-        <v>12.68819606910504</v>
+        <v>12.71459385993455</v>
       </c>
       <c r="N3" t="n">
-        <v>240.9174648583167</v>
+        <v>241.2364441523308</v>
       </c>
       <c r="O3" t="n">
-        <v>15.52151619070498</v>
+        <v>15.5317881827023</v>
       </c>
       <c r="P3" t="n">
-        <v>389.0064167624596</v>
+        <v>388.8254893917156</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26925,28 +27065,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.179546727240269</v>
+        <v>-0.163719761460458</v>
       </c>
       <c r="J4" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01709877407144067</v>
+        <v>0.01422645673033252</v>
       </c>
       <c r="M4" t="n">
-        <v>8.621828581435878</v>
+        <v>8.674121039035676</v>
       </c>
       <c r="N4" t="n">
-        <v>108.8204009888117</v>
+        <v>109.6190969677233</v>
       </c>
       <c r="O4" t="n">
-        <v>10.43170173024573</v>
+        <v>10.46991389495269</v>
       </c>
       <c r="P4" t="n">
-        <v>388.3714383816675</v>
+        <v>388.1999003907907</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27003,28 +27143,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6430376431066952</v>
+        <v>-0.6247010641379791</v>
       </c>
       <c r="J5" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1711099727808835</v>
+        <v>0.1623368207966457</v>
       </c>
       <c r="M5" t="n">
-        <v>8.837352866246508</v>
+        <v>8.89661182868473</v>
       </c>
       <c r="N5" t="n">
-        <v>117.7933950690889</v>
+        <v>119.0263285957711</v>
       </c>
       <c r="O5" t="n">
-        <v>10.85326656215026</v>
+        <v>10.90991881710268</v>
       </c>
       <c r="P5" t="n">
-        <v>389.9178608150847</v>
+        <v>389.7198030986593</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27081,28 +27221,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4457701458317324</v>
+        <v>-0.4302133675111295</v>
       </c>
       <c r="J6" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08500847736118899</v>
+        <v>0.07963479475015733</v>
       </c>
       <c r="M6" t="n">
-        <v>8.671974896812594</v>
+        <v>8.708293293389335</v>
       </c>
       <c r="N6" t="n">
-        <v>125.6408237792978</v>
+        <v>126.305133303393</v>
       </c>
       <c r="O6" t="n">
-        <v>11.20896176188044</v>
+        <v>11.23855565913134</v>
       </c>
       <c r="P6" t="n">
-        <v>377.6250224857647</v>
+        <v>377.4571571568728</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27159,28 +27299,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2445117671453497</v>
+        <v>-0.2398297217564272</v>
       </c>
       <c r="J7" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02811419421247519</v>
+        <v>0.02732646290063412</v>
       </c>
       <c r="M7" t="n">
-        <v>8.131578331246077</v>
+        <v>8.11963726556777</v>
       </c>
       <c r="N7" t="n">
-        <v>123.4454789495738</v>
+        <v>122.9087540489301</v>
       </c>
       <c r="O7" t="n">
-        <v>11.11060209662707</v>
+        <v>11.08642205803704</v>
       </c>
       <c r="P7" t="n">
-        <v>358.8039903559766</v>
+        <v>358.7540558303776</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27237,28 +27377,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.141560730940749</v>
+        <v>-0.1375605699593579</v>
       </c>
       <c r="J8" t="n">
+        <v>374</v>
+      </c>
+      <c r="K8" t="n">
         <v>372</v>
       </c>
-      <c r="K8" t="n">
-        <v>370</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0093508789828054</v>
+        <v>0.008920461713717187</v>
       </c>
       <c r="M8" t="n">
-        <v>8.589767536107662</v>
+        <v>8.567362808305791</v>
       </c>
       <c r="N8" t="n">
-        <v>125.6820127303626</v>
+        <v>125.0968204952525</v>
       </c>
       <c r="O8" t="n">
-        <v>11.2107989336337</v>
+        <v>11.18466899354883</v>
       </c>
       <c r="P8" t="n">
-        <v>369.2567005223348</v>
+        <v>369.2137554142011</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27315,28 +27455,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.379900292228966</v>
+        <v>-0.3736623452511604</v>
       </c>
       <c r="J9" t="n">
+        <v>374</v>
+      </c>
+      <c r="K9" t="n">
         <v>372</v>
       </c>
-      <c r="K9" t="n">
-        <v>370</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09459330401067612</v>
+        <v>0.09244762607311607</v>
       </c>
       <c r="M9" t="n">
-        <v>7.172589688518142</v>
+        <v>7.169530339663295</v>
       </c>
       <c r="N9" t="n">
-        <v>81.77916547360628</v>
+        <v>81.55897636239531</v>
       </c>
       <c r="O9" t="n">
-        <v>9.043183370561845</v>
+        <v>9.03100085053674</v>
       </c>
       <c r="P9" t="n">
-        <v>375.790858568993</v>
+        <v>375.7238937771969</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27393,28 +27533,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05316735350671076</v>
+        <v>0.05626120483536748</v>
       </c>
       <c r="J10" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008710809265974895</v>
+        <v>0.0009852706014193968</v>
       </c>
       <c r="M10" t="n">
-        <v>10.63099648615573</v>
+        <v>10.59286091074881</v>
       </c>
       <c r="N10" t="n">
-        <v>193.6596634289099</v>
+        <v>192.6759695686584</v>
       </c>
       <c r="O10" t="n">
-        <v>13.91616554331364</v>
+        <v>13.88077698000578</v>
       </c>
       <c r="P10" t="n">
-        <v>358.5050679577004</v>
+        <v>358.4720709472541</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27471,28 +27611,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06658123907745341</v>
+        <v>-0.05832595672656966</v>
       </c>
       <c r="J11" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K11" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003933971010832149</v>
+        <v>0.0003049320869378258</v>
       </c>
       <c r="M11" t="n">
-        <v>17.08829505142693</v>
+        <v>17.02888190538751</v>
       </c>
       <c r="N11" t="n">
-        <v>657.2347139503055</v>
+        <v>654.0322822474806</v>
       </c>
       <c r="O11" t="n">
-        <v>25.63658935877207</v>
+        <v>25.57405486518477</v>
       </c>
       <c r="P11" t="n">
-        <v>361.7374734216108</v>
+        <v>361.6476187002813</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27549,28 +27689,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4031256063024439</v>
+        <v>-0.389069489576908</v>
       </c>
       <c r="J12" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K12" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05054810782621555</v>
+        <v>0.04744180481575244</v>
       </c>
       <c r="M12" t="n">
-        <v>10.84145878195457</v>
+        <v>10.8481406181857</v>
       </c>
       <c r="N12" t="n">
-        <v>179.0300235696077</v>
+        <v>179.1652977615732</v>
       </c>
       <c r="O12" t="n">
-        <v>13.38021014669081</v>
+        <v>13.38526420215803</v>
       </c>
       <c r="P12" t="n">
-        <v>371.7582745122489</v>
+        <v>371.6059154128635</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27627,28 +27767,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01410509615122736</v>
+        <v>0.02262577142730756</v>
       </c>
       <c r="J13" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K13" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001098654980596914</v>
+        <v>0.0002845333241335846</v>
       </c>
       <c r="M13" t="n">
-        <v>8.070996314064912</v>
+        <v>8.072710096388182</v>
       </c>
       <c r="N13" t="n">
-        <v>108.288221227402</v>
+        <v>108.1181268862126</v>
       </c>
       <c r="O13" t="n">
-        <v>10.40616265620531</v>
+        <v>10.39798667465066</v>
       </c>
       <c r="P13" t="n">
-        <v>371.5407526952428</v>
+        <v>371.4499258738691</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27705,28 +27845,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2933290849157767</v>
+        <v>-0.2866686705386315</v>
       </c>
       <c r="J14" t="n">
+        <v>374</v>
+      </c>
+      <c r="K14" t="n">
         <v>372</v>
       </c>
-      <c r="K14" t="n">
-        <v>370</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.03390955361785586</v>
+        <v>0.03277646686916547</v>
       </c>
       <c r="M14" t="n">
-        <v>9.581378896028422</v>
+        <v>9.567270701297026</v>
       </c>
       <c r="N14" t="n">
-        <v>146.5633417322157</v>
+        <v>145.7359980882915</v>
       </c>
       <c r="O14" t="n">
-        <v>12.10633477697588</v>
+        <v>12.07211655379004</v>
       </c>
       <c r="P14" t="n">
-        <v>373.0659444329151</v>
+        <v>372.9949104686738</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27783,28 +27923,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2104564479377788</v>
+        <v>-0.2018613348509035</v>
       </c>
       <c r="J15" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K15" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01454153987869722</v>
+        <v>0.01352534922587223</v>
       </c>
       <c r="M15" t="n">
-        <v>9.925884863794446</v>
+        <v>9.918985682498695</v>
       </c>
       <c r="N15" t="n">
-        <v>176.8403609969748</v>
+        <v>175.9846582201477</v>
       </c>
       <c r="O15" t="n">
-        <v>13.2981337411298</v>
+        <v>13.26592093373648</v>
       </c>
       <c r="P15" t="n">
-        <v>378.1755681223383</v>
+        <v>378.0826967264264</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27861,28 +28001,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.40622032704833</v>
+        <v>-0.3905280621057418</v>
       </c>
       <c r="J16" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K16" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05894877434232537</v>
+        <v>0.05480683024520605</v>
       </c>
       <c r="M16" t="n">
-        <v>10.25709645647706</v>
+        <v>10.28259772250217</v>
       </c>
       <c r="N16" t="n">
-        <v>155.4194287358219</v>
+        <v>155.959093223153</v>
       </c>
       <c r="O16" t="n">
-        <v>12.46673288138564</v>
+        <v>12.4883583077662</v>
       </c>
       <c r="P16" t="n">
-        <v>386.009175765911</v>
+        <v>385.8396561370498</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27939,28 +28079,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7278416037134913</v>
+        <v>-0.7297045203579011</v>
       </c>
       <c r="J17" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K17" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02567599391390074</v>
+        <v>0.02608023397637604</v>
       </c>
       <c r="M17" t="n">
-        <v>21.66002447968877</v>
+        <v>21.53302963578021</v>
       </c>
       <c r="N17" t="n">
-        <v>1185.688105705384</v>
+        <v>1178.735254270589</v>
       </c>
       <c r="O17" t="n">
-        <v>34.43382211874516</v>
+        <v>34.33271405337174</v>
       </c>
       <c r="P17" t="n">
-        <v>371.2574949494413</v>
+        <v>371.2775051055837</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27998,7 +28138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R373"/>
+  <dimension ref="A1:R375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61941,7 +62081,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>-37.77574809565626,174.8332979885232</t>
+          <t>-37.775741044309996,174.83334656287087</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -62001,12 +62141,12 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>-37.7672478538016,174.83224623039726</t>
+          <t>-37.7672387888891,174.83231405952424</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>-37.766560948615165,174.83200322981548</t>
+          <t>-37.76655108029256,174.83207606727322</t>
         </is>
       </c>
       <c r="P373" t="inlineStr">
@@ -62016,10 +62156,194 @@
       </c>
       <c r="Q373" t="inlineStr">
         <is>
-          <t>-37.76512005425034,174.83201323824582</t>
+          <t>-37.76510787069877,174.83209535315413</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-37.775738937007254,174.83336107934065</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-37.775028075026476,174.83328533484902</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-37.774312966628806,174.83323294981528</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-37.773588633104524,174.8331695021238</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-37.77286113329946,174.83320017878683</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-37.772131043906924,174.83339712681487</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-37.77144239448407,174.83315450782536</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-37.770747229599515,174.83298379143548</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-37.770031491502145,174.8329431967769</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-37.76933152288038,174.83277797512895</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-37.76863209483021,174.83260746066284</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-37.76793785767207,174.8324370828113</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>-37.76723320931153,174.83235580912637</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-37.766545895994646,174.83211433210425</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>-37.76585678355807,174.8319033390925</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>-37.76509825293671,174.8321601748206</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-37.77573956919826,174.83335672439978</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-37.77503006885382,174.8332716001653</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-37.77431376717153,174.8332273643848</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-37.77358755459699,174.833179169311</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-37.7728608279278,174.833203904905</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-37.772131106634696,174.83339645034437</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-37.771443026785334,174.83314923262313</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-37.77074698566432,174.83298558140288</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-37.77003173894382,174.83294117754127</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-37.76933257961649,174.83276773208783</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>-37.76863415929475,174.83258628051922</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>-37.76793777983943,174.83243775674885</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>-37.767230965509455,174.8323725985087</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-37.76654428916297,174.832126191963</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>-37.76585619320105,174.83190747230643</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>-37.76509436278198,174.83218639356176</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R375"/>
+  <dimension ref="A1:R376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22817,6 +22817,66 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>408.87</v>
+      </c>
+      <c r="C376" t="n">
+        <v>403.76</v>
+      </c>
+      <c r="D376" t="n">
+        <v>394.09</v>
+      </c>
+      <c r="E376" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="F376" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="G376" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="H376" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="I376" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="J376" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="K376" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="L376" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="M376" t="n">
+        <v>376.11</v>
+      </c>
+      <c r="N376" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="O376" t="n">
+        <v>379.92</v>
+      </c>
+      <c r="P376" t="n">
+        <v>387.68</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22828,7 +22888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26741,6 +26801,16 @@
       </c>
       <c r="B391" t="n">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -26909,28 +26979,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1906577219067555</v>
+        <v>-0.1823905999186485</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01054686458394261</v>
+        <v>0.009674074838656677</v>
       </c>
       <c r="M2" t="n">
-        <v>11.81227174200878</v>
+        <v>11.83012518979731</v>
       </c>
       <c r="N2" t="n">
-        <v>205.4601274919334</v>
+        <v>205.6933710786138</v>
       </c>
       <c r="O2" t="n">
-        <v>14.33388040594498</v>
+        <v>14.34201419182863</v>
       </c>
       <c r="P2" t="n">
-        <v>396.8803536377541</v>
+        <v>396.7916999548385</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26987,28 +27057,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1029770267865945</v>
+        <v>0.1088755088325254</v>
       </c>
       <c r="J3" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002629358900276935</v>
+        <v>0.002948909738670014</v>
       </c>
       <c r="M3" t="n">
-        <v>12.71459385993455</v>
+        <v>12.71299763896486</v>
       </c>
       <c r="N3" t="n">
-        <v>241.2364441523308</v>
+        <v>240.979060889722</v>
       </c>
       <c r="O3" t="n">
-        <v>15.5317881827023</v>
+        <v>15.5235002782788</v>
       </c>
       <c r="P3" t="n">
-        <v>388.8254893917156</v>
+        <v>388.7620266850214</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27065,28 +27135,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.163719761460458</v>
+        <v>-0.1586263020431477</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01422645673033252</v>
+        <v>0.01340173001207445</v>
       </c>
       <c r="M4" t="n">
-        <v>8.674121039035676</v>
+        <v>8.683205093168278</v>
       </c>
       <c r="N4" t="n">
-        <v>109.6190969677233</v>
+        <v>109.6087137781919</v>
       </c>
       <c r="O4" t="n">
-        <v>10.46991389495269</v>
+        <v>10.46941802480882</v>
       </c>
       <c r="P4" t="n">
-        <v>388.1999003907907</v>
+        <v>388.1444066813709</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27143,28 +27213,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6247010641379791</v>
+        <v>-0.6187536453281904</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1623368207966457</v>
+        <v>0.1600189433874033</v>
       </c>
       <c r="M5" t="n">
-        <v>8.89661182868473</v>
+        <v>8.907048343924181</v>
       </c>
       <c r="N5" t="n">
-        <v>119.0263285957711</v>
+        <v>119.0979818619497</v>
       </c>
       <c r="O5" t="n">
-        <v>10.90991881710268</v>
+        <v>10.91320218185065</v>
       </c>
       <c r="P5" t="n">
-        <v>389.7198030986593</v>
+        <v>389.6552267564168</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27221,28 +27291,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4302133675111295</v>
+        <v>-0.4246277631653826</v>
       </c>
       <c r="J6" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K6" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07963479475015733</v>
+        <v>0.07792423205210941</v>
       </c>
       <c r="M6" t="n">
-        <v>8.708293293389335</v>
+        <v>8.715045179203974</v>
       </c>
       <c r="N6" t="n">
-        <v>126.305133303393</v>
+        <v>126.3113448935187</v>
       </c>
       <c r="O6" t="n">
-        <v>11.23855565913134</v>
+        <v>11.23883200753168</v>
       </c>
       <c r="P6" t="n">
-        <v>377.4571571568728</v>
+        <v>377.3965724810192</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27299,28 +27369,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2398297217564272</v>
+        <v>-0.238634904543379</v>
       </c>
       <c r="J7" t="n">
+        <v>375</v>
+      </c>
+      <c r="K7" t="n">
         <v>374</v>
       </c>
-      <c r="K7" t="n">
-        <v>373</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02732646290063412</v>
+        <v>0.02719731696478001</v>
       </c>
       <c r="M7" t="n">
-        <v>8.11963726556777</v>
+        <v>8.105914118990695</v>
       </c>
       <c r="N7" t="n">
-        <v>122.9087540489301</v>
+        <v>122.5964386860016</v>
       </c>
       <c r="O7" t="n">
-        <v>11.08642205803704</v>
+        <v>11.07232760922479</v>
       </c>
       <c r="P7" t="n">
-        <v>358.7540558303776</v>
+        <v>358.7412459462489</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27377,28 +27447,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1375605699593579</v>
+        <v>-0.1362350652978453</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008920461713717187</v>
+        <v>0.00879532947446493</v>
       </c>
       <c r="M8" t="n">
-        <v>8.567362808305791</v>
+        <v>8.552176724332176</v>
       </c>
       <c r="N8" t="n">
-        <v>125.0968204952525</v>
+        <v>124.7812736168008</v>
       </c>
       <c r="O8" t="n">
-        <v>11.18466899354883</v>
+        <v>11.17055386347521</v>
       </c>
       <c r="P8" t="n">
-        <v>369.2137554142011</v>
+        <v>369.1994514677119</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27455,28 +27525,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3736623452511604</v>
+        <v>-0.372158467048513</v>
       </c>
       <c r="J9" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09244762607311607</v>
+        <v>0.09218714191780819</v>
       </c>
       <c r="M9" t="n">
-        <v>7.169530339663295</v>
+        <v>7.158755566127113</v>
       </c>
       <c r="N9" t="n">
-        <v>81.55897636239531</v>
+        <v>81.36585004752686</v>
       </c>
       <c r="O9" t="n">
-        <v>9.03100085053674</v>
+        <v>9.020302104005545</v>
       </c>
       <c r="P9" t="n">
-        <v>375.7238937771969</v>
+        <v>375.7076649445405</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27533,28 +27603,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05626120483536748</v>
+        <v>0.05621947080195931</v>
       </c>
       <c r="J10" t="n">
+        <v>375</v>
+      </c>
+      <c r="K10" t="n">
         <v>374</v>
       </c>
-      <c r="K10" t="n">
-        <v>373</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0009852706014193968</v>
+        <v>0.0009889860782901216</v>
       </c>
       <c r="M10" t="n">
-        <v>10.59286091074881</v>
+        <v>10.56474602070075</v>
       </c>
       <c r="N10" t="n">
-        <v>192.6759695686584</v>
+        <v>192.1608130878166</v>
       </c>
       <c r="O10" t="n">
-        <v>13.88077698000578</v>
+        <v>13.86220808846183</v>
       </c>
       <c r="P10" t="n">
-        <v>358.4720709472541</v>
+        <v>358.4725183865162</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27611,28 +27681,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05832595672656966</v>
+        <v>-0.05711141140755985</v>
       </c>
       <c r="J11" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003049320869378258</v>
+        <v>0.0002939084665387615</v>
       </c>
       <c r="M11" t="n">
-        <v>17.02888190538751</v>
+        <v>16.98757022838994</v>
       </c>
       <c r="N11" t="n">
-        <v>654.0322822474806</v>
+        <v>652.2714028884515</v>
       </c>
       <c r="O11" t="n">
-        <v>25.57405486518477</v>
+        <v>25.53960459538188</v>
       </c>
       <c r="P11" t="n">
-        <v>361.6476187002813</v>
+        <v>361.6343307441612</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27689,28 +27759,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.389069489576908</v>
+        <v>-0.3848570213224772</v>
       </c>
       <c r="J12" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K12" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04744180481575244</v>
+        <v>0.04665232061548186</v>
       </c>
       <c r="M12" t="n">
-        <v>10.8481406181857</v>
+        <v>10.83813820507355</v>
       </c>
       <c r="N12" t="n">
-        <v>179.1652977615732</v>
+        <v>178.8781421104528</v>
       </c>
       <c r="O12" t="n">
-        <v>13.38526420215803</v>
+        <v>13.37453334178254</v>
       </c>
       <c r="P12" t="n">
-        <v>371.6059154128635</v>
+        <v>371.5600192590746</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27767,28 +27837,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02262577142730756</v>
+        <v>0.02458101841929215</v>
       </c>
       <c r="J13" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K13" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0002845333241335846</v>
+        <v>0.0003374552460065905</v>
       </c>
       <c r="M13" t="n">
-        <v>8.072710096388182</v>
+        <v>8.061294439929769</v>
       </c>
       <c r="N13" t="n">
-        <v>108.1181268862126</v>
+        <v>107.8710908648812</v>
       </c>
       <c r="O13" t="n">
-        <v>10.39798667465066</v>
+        <v>10.38610084992829</v>
       </c>
       <c r="P13" t="n">
-        <v>371.4499258738691</v>
+        <v>371.4289736438559</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27845,28 +27915,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2866686705386315</v>
+        <v>-0.284561080474383</v>
       </c>
       <c r="J14" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K14" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03277646686916547</v>
+        <v>0.03246625942679293</v>
       </c>
       <c r="M14" t="n">
-        <v>9.567270701297026</v>
+        <v>9.553546920057942</v>
       </c>
       <c r="N14" t="n">
-        <v>145.7359980882915</v>
+        <v>145.3958751691171</v>
       </c>
       <c r="O14" t="n">
-        <v>12.07211655379004</v>
+        <v>12.05802119624597</v>
       </c>
       <c r="P14" t="n">
-        <v>372.9949104686738</v>
+        <v>372.9723435194796</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27923,28 +27993,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2018613348509035</v>
+        <v>-0.1982884506048077</v>
       </c>
       <c r="J15" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K15" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01352534922587223</v>
+        <v>0.01311459161009809</v>
       </c>
       <c r="M15" t="n">
-        <v>9.918985682498695</v>
+        <v>9.911867468989845</v>
       </c>
       <c r="N15" t="n">
-        <v>175.9846582201477</v>
+        <v>175.6522897720872</v>
       </c>
       <c r="O15" t="n">
-        <v>13.26592093373648</v>
+        <v>13.25338786016946</v>
       </c>
       <c r="P15" t="n">
-        <v>378.0826967264264</v>
+        <v>378.0439320063698</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28001,28 +28071,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3905280621057418</v>
+        <v>-0.3844488903808547</v>
       </c>
       <c r="J16" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K16" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05480683024520605</v>
+        <v>0.05333439939184559</v>
       </c>
       <c r="M16" t="n">
-        <v>10.28259772250217</v>
+        <v>10.28622673808856</v>
       </c>
       <c r="N16" t="n">
-        <v>155.959093223153</v>
+        <v>155.9517138298198</v>
       </c>
       <c r="O16" t="n">
-        <v>12.4883583077662</v>
+        <v>12.48806285337401</v>
       </c>
       <c r="P16" t="n">
-        <v>385.8396561370498</v>
+        <v>385.7736371371643</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28079,28 +28149,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7297045203579011</v>
+        <v>-0.7310559595213485</v>
       </c>
       <c r="J17" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K17" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02608023397637604</v>
+        <v>0.02630897624627249</v>
       </c>
       <c r="M17" t="n">
-        <v>21.53302963578021</v>
+        <v>21.48314897147549</v>
       </c>
       <c r="N17" t="n">
-        <v>1178.735254270589</v>
+        <v>1175.543929146238</v>
       </c>
       <c r="O17" t="n">
-        <v>34.33271405337174</v>
+        <v>34.2862061060456</v>
       </c>
       <c r="P17" t="n">
-        <v>371.2775051055837</v>
+        <v>371.2921789598616</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28138,7 +28208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R375"/>
+  <dimension ref="A1:R376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62349,6 +62419,98 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-37.775729259601995,174.8334277434249</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-37.775020958832975,174.83333435538037</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-37.77430454490345,174.83329170853577</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-37.773580105349055,174.83324594033954</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-37.77285700614526,174.8332505378351</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-37.77212862888478,174.8334231709293</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-37.77144088772268,174.83316707851966</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>-37.77074210695455,174.8330213807482</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-37.77002714752052,174.8329786455781</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-37.7693253101832,174.83283819519917</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>-37.7686269995399,174.8326597350541</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>-37.76793179968713,174.83248953760994</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>-37.767223890038075,174.83242554102029</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>-37.766538089207025,174.83217195311076</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>-37.76585100762651,174.8319437775609</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>-37.76508866824719,174.8322247733307</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
